--- a/artfynd/A 14504-2023 artfynd.xlsx
+++ b/artfynd/A 14504-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -979,6 +979,108 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122907449</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91354</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skärlötamarken, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>563174</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6504094</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14504-2023 artfynd.xlsx
+++ b/artfynd/A 14504-2023 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>122907449</v>
       </c>
       <c r="B5" t="n">
-        <v>91354</v>
+        <v>91362</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 14504-2023 artfynd.xlsx
+++ b/artfynd/A 14504-2023 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>122907449</v>
       </c>
       <c r="B5" t="n">
-        <v>91362</v>
+        <v>91365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 14504-2023 artfynd.xlsx
+++ b/artfynd/A 14504-2023 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>122907449</v>
       </c>
       <c r="B5" t="n">
-        <v>91365</v>
+        <v>91367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 14504-2023 artfynd.xlsx
+++ b/artfynd/A 14504-2023 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>122907449</v>
       </c>
       <c r="B5" t="n">
-        <v>91367</v>
+        <v>91373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 14504-2023 artfynd.xlsx
+++ b/artfynd/A 14504-2023 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>122907449</v>
       </c>
       <c r="B5" t="n">
-        <v>91376</v>
+        <v>91393</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
